--- a/data/safeCities_eiu.xlsx
+++ b/data/safeCities_eiu.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/josemanuelmagallanes/UMASS/DVIZ690/tabular_multivar/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/josemanuelmagallanes/UMASS/DVIZ690/tabular_multivar/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{828EB67D-E2F6-D040-88EF-4B1F91794173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F6CFE6A-F0B1-914A-BEC2-FB86C8958030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3260" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{D46E0E18-3B36-C642-8C80-FA6A1D39BEE7}"/>
   </bookViews>
@@ -1249,7 +1249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBE8A4CB-1CD1-DC40-B520-0251022D3EC3}">
-  <dimension ref="A1:BK62"/>
+  <dimension ref="A1:BK61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.2">
@@ -12901,194 +12901,6 @@
       </c>
       <c r="BK61">
         <v>76.3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:63" x14ac:dyDescent="0.2">
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62">
-        <v>2</v>
-      </c>
-      <c r="D62">
-        <v>3</v>
-      </c>
-      <c r="E62">
-        <v>4</v>
-      </c>
-      <c r="F62">
-        <v>5</v>
-      </c>
-      <c r="G62">
-        <v>6</v>
-      </c>
-      <c r="H62">
-        <v>7</v>
-      </c>
-      <c r="I62">
-        <v>8</v>
-      </c>
-      <c r="J62">
-        <v>9</v>
-      </c>
-      <c r="K62">
-        <v>10</v>
-      </c>
-      <c r="L62">
-        <v>11</v>
-      </c>
-      <c r="M62">
-        <v>12</v>
-      </c>
-      <c r="N62">
-        <v>13</v>
-      </c>
-      <c r="O62">
-        <v>14</v>
-      </c>
-      <c r="P62">
-        <v>15</v>
-      </c>
-      <c r="Q62">
-        <v>16</v>
-      </c>
-      <c r="R62">
-        <v>17</v>
-      </c>
-      <c r="S62">
-        <v>18</v>
-      </c>
-      <c r="T62">
-        <v>19</v>
-      </c>
-      <c r="U62">
-        <v>20</v>
-      </c>
-      <c r="V62">
-        <v>21</v>
-      </c>
-      <c r="W62">
-        <v>22</v>
-      </c>
-      <c r="X62">
-        <v>23</v>
-      </c>
-      <c r="Y62">
-        <v>24</v>
-      </c>
-      <c r="Z62">
-        <v>25</v>
-      </c>
-      <c r="AA62">
-        <v>26</v>
-      </c>
-      <c r="AB62">
-        <v>27</v>
-      </c>
-      <c r="AC62">
-        <v>28</v>
-      </c>
-      <c r="AD62">
-        <v>29</v>
-      </c>
-      <c r="AE62">
-        <v>30</v>
-      </c>
-      <c r="AF62">
-        <v>31</v>
-      </c>
-      <c r="AG62">
-        <v>32</v>
-      </c>
-      <c r="AH62">
-        <v>33</v>
-      </c>
-      <c r="AI62">
-        <v>34</v>
-      </c>
-      <c r="AJ62">
-        <v>35</v>
-      </c>
-      <c r="AK62">
-        <v>36</v>
-      </c>
-      <c r="AL62">
-        <v>37</v>
-      </c>
-      <c r="AM62">
-        <v>38</v>
-      </c>
-      <c r="AN62">
-        <v>39</v>
-      </c>
-      <c r="AO62">
-        <v>40</v>
-      </c>
-      <c r="AP62">
-        <v>41</v>
-      </c>
-      <c r="AQ62">
-        <v>42</v>
-      </c>
-      <c r="AR62">
-        <v>43</v>
-      </c>
-      <c r="AS62">
-        <v>44</v>
-      </c>
-      <c r="AT62">
-        <v>45</v>
-      </c>
-      <c r="AU62">
-        <v>46</v>
-      </c>
-      <c r="AV62">
-        <v>47</v>
-      </c>
-      <c r="AW62">
-        <v>48</v>
-      </c>
-      <c r="AX62">
-        <v>49</v>
-      </c>
-      <c r="AY62">
-        <v>50</v>
-      </c>
-      <c r="AZ62">
-        <v>51</v>
-      </c>
-      <c r="BA62">
-        <v>52</v>
-      </c>
-      <c r="BB62">
-        <v>53</v>
-      </c>
-      <c r="BC62">
-        <v>54</v>
-      </c>
-      <c r="BD62">
-        <v>55</v>
-      </c>
-      <c r="BE62">
-        <v>56</v>
-      </c>
-      <c r="BF62">
-        <v>57</v>
-      </c>
-      <c r="BG62">
-        <v>58</v>
-      </c>
-      <c r="BH62">
-        <v>59</v>
-      </c>
-      <c r="BI62">
-        <v>60</v>
-      </c>
-      <c r="BJ62">
-        <v>61</v>
-      </c>
-      <c r="BK62">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
